--- a/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_sensor_profile_summary.xlsx
+++ b/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_sensor_profile_summary.xlsx
@@ -439,7 +439,7 @@
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="19" customWidth="1" min="13" max="13"/>
@@ -567,29 +567,29 @@
         <v>6144</v>
       </c>
       <c r="F2" t="n">
-        <v>3.070830773783034</v>
+        <v>2.991365026900263</v>
       </c>
       <c r="G2" t="n">
-        <v>1.719170654683633</v>
+        <v>1.397118149642645</v>
       </c>
       <c r="H2" t="n">
-        <v>2.841685845876715</v>
+        <v>2.882216365351717</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5458984375</v>
+        <v>0.5384114583333334</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>0.1236979166666667</v>
       </c>
       <c r="K2" t="n">
-        <v>0.08040364583333333</v>
+        <v>0.1551106770833333</v>
       </c>
       <c r="L2" t="n">
         <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>rep</t>
+          <t>rank</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -598,13 +598,13 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>0.3727514274569134</v>
+        <v>0.3671966917553123</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9834545159639517</v>
+        <v>0.9846511314191306</v>
       </c>
       <c r="Q2" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -637,22 +637,22 @@
         <v>6144</v>
       </c>
       <c r="F3" t="n">
-        <v>3.142157488652446</v>
+        <v>3.021774822649508</v>
       </c>
       <c r="G3" t="n">
-        <v>1.373720403462665</v>
+        <v>1.086101793322395</v>
       </c>
       <c r="H3" t="n">
-        <v>3.229846423837018</v>
+        <v>3.127596142511146</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4264322916666667</v>
+        <v>0.45849609375</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>0.1236979166666667</v>
       </c>
       <c r="K3" t="n">
-        <v>0.06803385416666667</v>
+        <v>0.1551106770833333</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
@@ -668,13 +668,13 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>0.3399081867238374</v>
+        <v>0.3565396266980197</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9328829073931613</v>
+        <v>0.96742626498364</v>
       </c>
       <c r="Q3" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -707,22 +707,22 @@
         <v>6144</v>
       </c>
       <c r="F4" t="n">
-        <v>3.18164127197674</v>
+        <v>3.131028154293658</v>
       </c>
       <c r="G4" t="n">
-        <v>1.232099210292466</v>
+        <v>1.078047934194857</v>
       </c>
       <c r="H4" t="n">
-        <v>3.298856604128352</v>
+        <v>3.262056983560528</v>
       </c>
       <c r="I4" t="n">
-        <v>0.408203125</v>
+        <v>0.4124348958333333</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>0.1236979166666667</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1139322916666667</v>
+        <v>0.1551106770833333</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
@@ -738,13 +738,13 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>0.3353033965361593</v>
+        <v>0.3509423129858495</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9029825838306728</v>
+        <v>0.935613074451222</v>
       </c>
       <c r="Q4" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -777,22 +777,22 @@
         <v>6144</v>
       </c>
       <c r="F5" t="n">
-        <v>2.906602423675531</v>
+        <v>2.86307478202277</v>
       </c>
       <c r="G5" t="n">
-        <v>1.465895285382</v>
+        <v>1.380703795158853</v>
       </c>
       <c r="H5" t="n">
-        <v>2.857091979771599</v>
+        <v>2.852778774835314</v>
       </c>
       <c r="I5" t="n">
-        <v>0.55615234375</v>
+        <v>0.5769856770833334</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>0.1236979166666667</v>
       </c>
       <c r="K5" t="n">
-        <v>0.10986328125</v>
+        <v>0.1551106770833333</v>
       </c>
       <c r="L5" t="n">
         <v>1</v>
@@ -808,13 +808,13 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>0.292126328018068</v>
+        <v>0.3173637077884937</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9952558460302097</v>
+        <v>0.9897570360949748</v>
       </c>
       <c r="Q5" t="n">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -847,22 +847,22 @@
         <v>6144</v>
       </c>
       <c r="F6" t="n">
-        <v>3.272407017896344</v>
+        <v>3.182787241925622</v>
       </c>
       <c r="G6" t="n">
-        <v>1.573528210048874</v>
+        <v>1.400992172975753</v>
       </c>
       <c r="H6" t="n">
-        <v>3.396879687043599</v>
+        <v>3.315822347149703</v>
       </c>
       <c r="I6" t="n">
-        <v>0.39501953125</v>
+        <v>0.4168294270833333</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.1236979166666667</v>
       </c>
       <c r="K6" t="n">
-        <v>0.09065755208333333</v>
+        <v>0.1551106770833333</v>
       </c>
       <c r="L6" t="n">
         <v>1</v>
@@ -878,13 +878,13 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>0.3097116884871243</v>
+        <v>0.3119088446938602</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8846468678308574</v>
+        <v>0.8603013852957601</v>
       </c>
       <c r="Q6" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -917,22 +917,22 @@
         <v>6144</v>
       </c>
       <c r="F7" t="n">
-        <v>3.259813282127145</v>
+        <v>3.338005309442631</v>
       </c>
       <c r="G7" t="n">
-        <v>1.727339701482</v>
+        <v>1.72430220500453</v>
       </c>
       <c r="H7" t="n">
-        <v>3.244276024843844</v>
+        <v>3.442659224238525</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3902994791666667</v>
+        <v>0.37109375</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>0.1236979166666667</v>
       </c>
       <c r="K7" t="n">
-        <v>0.11669921875</v>
+        <v>0.1551106770833333</v>
       </c>
       <c r="L7" t="n">
         <v>1</v>
@@ -948,13 +948,13 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>0.2613654739888597</v>
+        <v>0.2566875909395006</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8268812385656104</v>
+        <v>0.8515636606093461</v>
       </c>
       <c r="Q7" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -987,22 +987,22 @@
         <v>6144</v>
       </c>
       <c r="F8" t="n">
-        <v>3.353332398413104</v>
+        <v>3.207627583942782</v>
       </c>
       <c r="G8" t="n">
-        <v>1.479754756704863</v>
+        <v>1.424133990353387</v>
       </c>
       <c r="H8" t="n">
-        <v>3.630840875999072</v>
+        <v>3.446181960850001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3455403645833333</v>
+        <v>0.39892578125</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.1236979166666667</v>
       </c>
       <c r="K8" t="n">
-        <v>0.09830729166666667</v>
+        <v>0.1551106770833333</v>
       </c>
       <c r="L8" t="n">
         <v>1</v>
@@ -1018,13 +1018,13 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>0.3335564940067324</v>
+        <v>0.3613301963721832</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9309481803314158</v>
+        <v>0.9422517723144715</v>
       </c>
       <c r="Q8" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1057,22 +1057,22 @@
         <v>6144</v>
       </c>
       <c r="F9" t="n">
-        <v>3.30148052689994</v>
+        <v>3.330419747482324</v>
       </c>
       <c r="G9" t="n">
-        <v>1.931726233822614</v>
+        <v>1.76876468494126</v>
       </c>
       <c r="H9" t="n">
-        <v>3.296514610246018</v>
+        <v>3.387398510726662</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3649088541666667</v>
+        <v>0.3636067708333333</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.1236979166666667</v>
       </c>
       <c r="K9" t="n">
-        <v>0.09684244791666667</v>
+        <v>0.1551106770833333</v>
       </c>
       <c r="L9" t="n">
         <v>1</v>
@@ -1088,13 +1088,13 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>0.3010477525234481</v>
+        <v>0.2386717242157183</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9941193908629035</v>
+        <v>0.9927228781839712</v>
       </c>
       <c r="Q9" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1127,22 +1127,22 @@
         <v>6144</v>
       </c>
       <c r="F10" t="n">
-        <v>2.965146451460984</v>
+        <v>2.953297581062933</v>
       </c>
       <c r="G10" t="n">
-        <v>1.594949133423092</v>
+        <v>1.443202150098335</v>
       </c>
       <c r="H10" t="n">
-        <v>2.972420071811874</v>
+        <v>3.05703006281439</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5040690104166666</v>
+        <v>0.47314453125</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1915690104166667</v>
+        <v>0.1551106770833333</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
@@ -1158,13 +1158,13 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>0.3792548317108603</v>
+        <v>0.3979515850319885</v>
       </c>
       <c r="P10" t="n">
-        <v>0.788885860502892</v>
+        <v>0.8021441925365111</v>
       </c>
       <c r="Q10" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1197,29 +1197,29 @@
         <v>6144</v>
       </c>
       <c r="F11" t="n">
-        <v>2.975938411955505</v>
+        <v>2.847512472360304</v>
       </c>
       <c r="G11" t="n">
-        <v>1.407242478501339</v>
+        <v>1.196673476378269</v>
       </c>
       <c r="H11" t="n">
-        <v>3.029451559971173</v>
+        <v>2.801079832059873</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4894205729166667</v>
+        <v>0.54248046875</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2195638020833333</v>
+        <v>0.1551106770833333</v>
       </c>
       <c r="L11" t="n">
         <v>1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>rank</t>
+          <t>rep</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1228,13 +1228,13 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>0.3872895580902494</v>
+        <v>0.4228056619979209</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9293453342105248</v>
+        <v>0.9641473741284977</v>
       </c>
       <c r="Q11" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -1267,22 +1267,22 @@
         <v>6144</v>
       </c>
       <c r="F12" t="n">
-        <v>3.13662924583125</v>
+        <v>3.004465039025623</v>
       </c>
       <c r="G12" t="n">
-        <v>1.234844350545314</v>
+        <v>1.256814836053059</v>
       </c>
       <c r="H12" t="n">
-        <v>3.345023360588775</v>
+        <v>3.103664225856462</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3942057291666667</v>
+        <v>0.46630859375</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2757161458333333</v>
+        <v>0.1551106770833333</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
@@ -1298,13 +1298,13 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>0.4348874558313881</v>
+        <v>0.4508076536311401</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9539520673912266</v>
+        <v>0.965228793471681</v>
       </c>
       <c r="Q12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -1337,22 +1337,22 @@
         <v>6144</v>
       </c>
       <c r="F13" t="n">
-        <v>3.26400216563733</v>
+        <v>3.278452162599093</v>
       </c>
       <c r="G13" t="n">
-        <v>1.641924145506589</v>
+        <v>1.635624496701244</v>
       </c>
       <c r="H13" t="n">
-        <v>3.322774652040114</v>
+        <v>3.178524039568874</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3995768229166667</v>
+        <v>0.45166015625</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2752278645833333</v>
+        <v>0.1551106770833333</v>
       </c>
       <c r="L13" t="n">
         <v>1</v>
@@ -1368,13 +1368,13 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>0.3721151656851289</v>
+        <v>0.3876397852298876</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9817698978159056</v>
+        <v>0.9329189858367722</v>
       </c>
       <c r="Q13" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -1407,29 +1407,29 @@
         <v>6144</v>
       </c>
       <c r="F14" t="n">
-        <v>3.447823426202767</v>
+        <v>3.232049044270422</v>
       </c>
       <c r="G14" t="n">
-        <v>2.361792795260897</v>
+        <v>2.070764355334329</v>
       </c>
       <c r="H14" t="n">
-        <v>3.505815896705697</v>
+        <v>3.178039621334407</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3111979166666667</v>
+        <v>0.4251302083333333</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3107096354166667</v>
+        <v>0.1551106770833333</v>
       </c>
       <c r="L14" t="n">
         <v>1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>gradient</t>
+          <t>rep</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1438,13 +1438,13 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>0.2993427536674755</v>
+        <v>0.3585446123753275</v>
       </c>
       <c r="P14" t="n">
-        <v>0.818359792679517</v>
+        <v>0.8290871408895601</v>
       </c>
       <c r="Q14" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -1477,29 +1477,29 @@
         <v>6144</v>
       </c>
       <c r="F15" t="n">
-        <v>2.892340745210469</v>
+        <v>2.97725611737502</v>
       </c>
       <c r="G15" t="n">
-        <v>1.223552635528877</v>
+        <v>1.332808827783482</v>
       </c>
       <c r="H15" t="n">
-        <v>2.643093082236648</v>
+        <v>2.875682717301182</v>
       </c>
       <c r="I15" t="n">
-        <v>0.60546875</v>
+        <v>0.5379231770833334</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.31640625</v>
+        <v>0.1551106770833333</v>
       </c>
       <c r="L15" t="n">
         <v>1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>rank</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1508,13 +1508,13 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>0.4205365108678497</v>
+        <v>0.4225899077971409</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9982032722377635</v>
+        <v>0.9912929060386587</v>
       </c>
       <c r="Q15" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>

--- a/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_sensor_profile_summary.xlsx
+++ b/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_sensor_profile_summary.xlsx
@@ -439,9 +439,9 @@
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
     <col width="19" customWidth="1" min="13" max="13"/>
     <col width="15" customWidth="1" min="14" max="14"/>
     <col width="21" customWidth="1" min="15" max="15"/>
@@ -579,13 +579,13 @@
         <v>0.5384114583333334</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1236979166666667</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0.1551106770833333</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0.4015299479166667</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -649,13 +649,13 @@
         <v>0.45849609375</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1236979166666667</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0.1551106770833333</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0.4015299479166667</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -719,13 +719,13 @@
         <v>0.4124348958333333</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1236979166666667</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>0.1551106770833333</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0.4015299479166667</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -789,13 +789,13 @@
         <v>0.5769856770833334</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1236979166666667</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0.1551106770833333</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0.4015299479166667</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -859,13 +859,13 @@
         <v>0.4168294270833333</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1236979166666667</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0.1551106770833333</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0.4015299479166667</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -929,13 +929,13 @@
         <v>0.37109375</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1236979166666667</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0.1551106770833333</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0.4015299479166667</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -999,13 +999,13 @@
         <v>0.39892578125</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1236979166666667</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0.1551106770833333</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0.4015299479166667</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1069,13 +1069,13 @@
         <v>0.3636067708333333</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1236979166666667</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0.1551106770833333</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0.4015299479166667</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>0.1551106770833333</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0.4015299479166667</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="O10" t="n">
@@ -1215,7 +1215,7 @@
         <v>0.1551106770833333</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0.4015299479166667</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="O11" t="n">
@@ -1285,7 +1285,7 @@
         <v>0.1551106770833333</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0.4015299479166667</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="O12" t="n">
@@ -1355,7 +1355,7 @@
         <v>0.1551106770833333</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0.4015299479166667</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="O13" t="n">
@@ -1425,7 +1425,7 @@
         <v>0.1551106770833333</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0.4015299479166667</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="O14" t="n">
@@ -1495,7 +1495,7 @@
         <v>0.1551106770833333</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0.4015299479166667</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="O15" t="n">

--- a/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_sensor_profile_summary.xlsx
+++ b/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_sensor_profile_summary.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="O3" t="n">
@@ -804,7 +804,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -874,7 +874,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="O6" t="n">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="O8" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="O9" t="n">
